--- a/observations/orbit_plans/mtp107/nomad_mtp107_plan_generic.xlsx
+++ b/observations/orbit_plans/mtp107/nomad_mtp107_plan_generic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iant\Documents\PROGRAMS\nomad_obs\observations\orbit_plans\mtp107\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DC9E62-AEC8-4857-9E5A-22FEB913521A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DABB74-2D36-47D3-9BA8-AF56D62C7005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1952,14 +1952,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M342"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="9.109375" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>14</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>14</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>14</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>14</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>47</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>14</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>14</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>14</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>14</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>14</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>14</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>14</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>47</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>14</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>14</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>14</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>14</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>14</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>14</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>14</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>14</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>47</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>14</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>14</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>14</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>47</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>14</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>14</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>14</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>14</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>14</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>3</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>14</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>14</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>14</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>14</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>14</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>14</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>14</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>14</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>14</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>14</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>14</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>14</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>14</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>14</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>14</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>47</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>14</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>7</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>14</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>3</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>14</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>14</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>14</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>14</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>3</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>14</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>14</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>14</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>28</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>14</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>14</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>1</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>1</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="128" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>7</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>1</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>14</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>14</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>1</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>1</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>14</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>1</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>14</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>14</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>1</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>14</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>1</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>1</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>14</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>14</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>1</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>14</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>14</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>14</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>1</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>1</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>14</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>14</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>1</v>
       </c>
@@ -4941,7 +4941,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>14</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>1</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>1</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>14</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>14</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>1</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>1</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>14</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>1</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>14</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>1</v>
       </c>
@@ -5229,7 +5229,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>14</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>1</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>1</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>14</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>1</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>3</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>14</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>14</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>14</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>1</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>14</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>1</v>
       </c>
@@ -5475,7 +5475,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>1</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>14</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>1</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>14</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>1</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>14</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>14</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>1</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>1</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>14</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>1</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>14</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>1</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>3</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>14</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>1</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>14</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>1</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>14</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>1</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>1</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>14</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>1</v>
       </c>
@@ -6135,16 +6135,16 @@
         <v>316</v>
       </c>
     </row>
-    <row r="205" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>28</v>
       </c>
+      <c r="H205" s="4" t="s">
+        <v>516</v>
+      </c>
       <c r="I205" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="J205" s="4" t="s">
-        <v>516</v>
-      </c>
       <c r="L205" s="4" t="s">
         <v>317</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>1</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>1</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>14</v>
       </c>
@@ -6221,7 +6221,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>1</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>14</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>1</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1</v>
       </c>
@@ -6325,7 +6325,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>14</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>1</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>14</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>1</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>14</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>1</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>14</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>1</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>14</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>1</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>14</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>1</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>1</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>14</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>1</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>14</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>1</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>14</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>1</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>14</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>1</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>14</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>1</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>14</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>14</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>14</v>
       </c>
@@ -6959,7 +6959,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>1</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>1</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>14</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>1</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>14</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>1</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>14</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>1</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>1</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>14</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>1</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>14</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>1</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>14</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>1</v>
       </c>
@@ -7336,7 +7336,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>14</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>14</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>1</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>1</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>14</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>1</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>14</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>1</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>14</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>1</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>1</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>14</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>1</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>3</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>1</v>
       </c>
@@ -7669,7 +7669,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>14</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>1</v>
       </c>
@@ -7715,7 +7715,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>1</v>
       </c>
@@ -7747,7 +7747,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>14</v>
       </c>
@@ -7761,7 +7761,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>1</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>14</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>1</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>1</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>14</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>1</v>
       </c>
@@ -7911,7 +7911,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>14</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>1</v>
       </c>
@@ -7957,7 +7957,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>1</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>14</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>1</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>14</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>1</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>3</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>1</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>1</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>14</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>1</v>
       </c>
@@ -8208,7 +8208,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>14</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>1</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>14</v>
       </c>
@@ -8268,7 +8268,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>1</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>1</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>14</v>
       </c>
@@ -8337,7 +8337,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>1</v>
       </c>
@@ -8369,7 +8369,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>14</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>14</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>1</v>
       </c>
@@ -8429,7 +8429,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>14</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>47</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>1</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>14</v>
       </c>
@@ -8500,7 +8500,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>1</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>1</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>14</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>14</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>14</v>
       </c>
@@ -8597,7 +8597,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>1</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>14</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>1</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>14</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>1</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>14</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>1</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>14</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="322" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
         <v>47</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>1</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>14</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>1</v>
       </c>
@@ -8861,7 +8861,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>14</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="327" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="3">
         <v>47</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>1</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>1</v>
       </c>
@@ -8941,7 +8941,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>3</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>1</v>
       </c>
@@ -8990,7 +8990,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>14</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>14</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>1</v>
       </c>
@@ -9050,7 +9050,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>1</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>14</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>1</v>
       </c>
@@ -9119,7 +9119,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>14</v>
       </c>
@@ -9133,7 +9133,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>14</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>1</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>1</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>14</v>
       </c>
